--- a/output/pdf_financials_xlsx/OCEN.xlsx
+++ b/output/pdf_financials_xlsx/OCEN.xlsx
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.305988</v>
+        <v>-1.305988</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>7.50603</v>
@@ -1241,16 +1241,16 @@
         <v>26.453954</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>6.54541</v>
+        <v>-6.54541</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-7.384012</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>3.286675</v>
+        <v>-3.286675</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>10.239997</v>
+        <v>-10.239997</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-4.544425</v>
@@ -1271,28 +1271,28 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-15.01206</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1.26</v>
+        <v>-9.35568</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.74</v>
+        <v>-6.566632</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.31</v>
+        <v>-7.576932</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.199</v>
+        <v>-17.214654</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.231106</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>1.679826</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-52.907908</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>-0</v>
@@ -1486,34 +1486,34 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.305988</v>
+        <v>-1.305988</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>7.50603</v>
+        <v>-7.50603</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5.30784</v>
+        <v>-5.30784</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.653316</v>
+        <v>-3.653316</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.943466</v>
+        <v>-3.943466</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>8.706827000000001</v>
+        <v>-8.706827000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.115553</v>
+        <v>-1.115553</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.839913</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>26.453954</v>
+        <v>-26.453954</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>6.54541</v>
+        <v>-6.54541</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-2.918392</v>
@@ -1648,43 +1648,43 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.305988</v>
+        <v>-1.305988</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>7.50603</v>
+        <v>-7.50603</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5.30784</v>
+        <v>-5.30784</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.653316</v>
+        <v>-3.653316</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.943466</v>
+        <v>-3.943466</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>8.706827000000001</v>
+        <v>-8.706827000000001</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.115553</v>
+        <v>-1.115553</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>0.839913</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>26.453954</v>
+        <v>-26.453954</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>6.54541</v>
+        <v>-6.54541</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-7.384012</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>3.286675</v>
+        <v>-3.286675</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>10.239997</v>
+        <v>-10.239997</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>-4.544425</v>
@@ -1822,22 +1822,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-32.6497</v>
+        <v>32.6497</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>53.6145</v>
+        <v>-53.6145</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>66.348</v>
+        <v>-66.348</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>91.3329</v>
+        <v>-91.3329</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>78.86932</v>
+        <v>-78.86932</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>108.835338</v>
+        <v>-108.835338</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>139.231337</v>
+        <v>-139.231337</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>130.9082</v>
+        <v>-130.9082</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>-184.6003</v>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.30912</v>
+        <v>-1.302856</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>7.533921</v>
@@ -1913,16 +1913,16 @@
         <v>26.882045</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>6.706906</v>
+        <v>-6.383914</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-7.457575</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>3.021137</v>
+        <v>-3.552213</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>9.941748</v>
+        <v>-10.538246</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-5.011917</v>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.30912</v>
+        <v>-1.302856</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>7.533921</v>
@@ -2021,16 +2021,16 @@
         <v>26.909517</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>6.738124</v>
+        <v>-6.352696</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-6.882685</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>3.117813</v>
+        <v>-3.455537</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>9.946210000000001</v>
+        <v>-10.533784</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-5.011917</v>
@@ -2130,43 +2130,43 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>31.12771255780861</v>
+        <v>231.1277125578086</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>25.40060879080745</v>
+        <v>225.4006087908075</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.531798563685474</v>
+        <v>208.5317985636855</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>2.339022643502271</v>
+        <v>202.3390226435023</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-200</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -5382,43 +5382,43 @@
         <v>0.07754999999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.366033</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>8.899330000000001</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>9.869761</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>9.972788</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>10.99021</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>10.924185</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>10.924185</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>11.155844</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>12.313973</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>13.12466</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>13.330449</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>14.419048</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>14.945073</v>
       </c>
     </row>
     <row r="93">
@@ -6690,22 +6690,22 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-8.85493</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.112802</v>
+        <v>-6.525873</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.987907</v>
+        <v>-2.732354</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>1.085996</v>
+        <v>-2.992626</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>1.1203</v>
+        <v>-1.972956</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.471937</v>
+        <v>-1.056855</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -8641,7 +8641,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -13258,7 +13262,11 @@
           <t>Reserves 11,155,844</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -27198,7 +27206,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -28719,7 +28731,11 @@
           <t>Net tax credit related to resources, government assistance and mining tax credit deducted from exploration and evaluation asset expenditures (Note 8)</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -31144,7 +31160,11 @@
           <t>credit deducted from exploration and evaluation asset expenditures (Note 7)</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -31686,7 +31706,11 @@
           <t>credit deducted from exploration and evaluation asset expenditures (Note 8)</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -32774,7 +32798,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -36781,10 +36809,10 @@
         </is>
       </c>
       <c r="Q328" s="5" t="n">
-        <v>3.286675</v>
+        <v>-3.286675</v>
       </c>
       <c r="R328" s="5" t="n">
-        <v>10.239997</v>
+        <v>-10.239997</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
@@ -38992,10 +39020,10 @@
         </is>
       </c>
       <c r="O353" s="5" t="n">
-        <v>6.54541</v>
+        <v>-6.54541</v>
       </c>
       <c r="P353" s="5" t="n">
-        <v>7.384012</v>
+        <v>-7.384012</v>
       </c>
       <c r="Q353" t="inlineStr">
         <is>
@@ -40298,10 +40326,10 @@
         </is>
       </c>
       <c r="N368" s="5" t="n">
-        <v>26.453954</v>
+        <v>-26.453954</v>
       </c>
       <c r="O368" s="5" t="n">
-        <v>6.54541</v>
+        <v>-6.54541</v>
       </c>
       <c r="P368" t="inlineStr">
         <is>
@@ -42962,19 +42990,19 @@
         </is>
       </c>
       <c r="H398" s="5" t="n">
-        <v>5.30784</v>
+        <v>-5.30784</v>
       </c>
       <c r="I398" s="5" t="n">
-        <v>3.653316</v>
+        <v>-3.653316</v>
       </c>
       <c r="J398" s="5" t="n">
-        <v>3.943466</v>
+        <v>-3.943466</v>
       </c>
       <c r="K398" s="5" t="n">
-        <v>8.706827000000001</v>
+        <v>-8.706827000000001</v>
       </c>
       <c r="L398" s="5" t="n">
-        <v>1.115553</v>
+        <v>-1.115553</v>
       </c>
       <c r="M398" t="inlineStr">
         <is>
@@ -44749,10 +44777,10 @@
         </is>
       </c>
       <c r="G418" s="5" t="n">
-        <v>7.50603</v>
+        <v>-7.50603</v>
       </c>
       <c r="H418" s="5" t="n">
-        <v>5.30784</v>
+        <v>-5.30784</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -45553,10 +45581,10 @@
         </is>
       </c>
       <c r="F427" s="5" t="n">
-        <v>1.305988</v>
+        <v>-1.305988</v>
       </c>
       <c r="G427" s="5" t="n">
-        <v>7.50603</v>
+        <v>-7.50603</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OCEN.xlsx
+++ b/output/pdf_financials_xlsx/OCEN.xlsx
@@ -2271,16 +2271,16 @@
         <v>0.295</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.580021</v>
+        <v>4.443806</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.950753</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>14.410142</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.655041</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>1.347003</v>
@@ -2292,25 +2292,25 @@
         <v>40.473219</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>40.473219</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>26.638101</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>20.125836</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>7.31699</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>7.581884</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5.494253</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>3.600401</v>
       </c>
     </row>
     <row r="35">
@@ -2375,16 +2375,16 @@
         <v>0.295</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.580021</v>
+        <v>4.443806</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.950753</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>14.410142</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.565487</v>
+        <v>7.220528</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>1.347003</v>
@@ -2396,25 +2396,25 @@
         <v>40.473219</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>40.473219</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>26.638101</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>20.125836</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>7.31699</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>7.581884</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>5.494253</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>3.600401</v>
       </c>
     </row>
     <row r="37">
@@ -2999,16 +2999,16 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.219035</v>
+        <v>0.35525</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>6.357272</v>
+        <v>1.406519</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>15.309077</v>
+        <v>0.898935</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5.868765</v>
+        <v>0.213724</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.213724</v>
@@ -3020,19 +3020,19 @@
         <v>0.068663</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>40.541882</v>
+        <v>0.068663</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>26.881101</v>
+        <v>0.243</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>20.352997</v>
+        <v>0.227161</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>20.546107</v>
+        <v>13.229117</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>7.62706</v>
+        <v>0.045176</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -16029,7 +16029,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -46128,7 +46128,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">

--- a/output/pdf_financials_xlsx/OCEN.xlsx
+++ b/output/pdf_financials_xlsx/OCEN.xlsx
@@ -1067,13 +1067,13 @@
         <v>-0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-4.163975</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>1.659095</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>2.424688</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>-0</v>
@@ -1901,13 +1901,13 @@
         <v>3.654315</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>8.629307000000001</v>
+        <v>12.793282</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.54575</v>
+        <v>-0.113345</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.335378</v>
+        <v>-2.760066</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>26.882045</v>
@@ -1970,10 +1970,10 @@
         <v>0.031218</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.57489</v>
+        <v>0.551796</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.096676</v>
+        <v>0.07882699999999999</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>0.004462</v>
@@ -2009,13 +2009,13 @@
         <v>3.654315</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8.629307000000001</v>
+        <v>12.793282</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.54575</v>
+        <v>-0.113345</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.317316</v>
+        <v>-2.742004</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>26.909517</v>
@@ -2024,10 +2024,10 @@
         <v>-6.352696</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.882685</v>
+        <v>-6.905779</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.455537</v>
+        <v>-3.473386</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-10.533784</v>
@@ -5784,10 +5784,10 @@
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.551796</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.07882699999999999</v>
       </c>
       <c r="O100" s="3" t="n">
         <v>0</v>
@@ -21807,7 +21807,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -38610,7 +38610,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -41084,7 +41084,11 @@
           <t>Net finance costs (Note 8)</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -42708,7 +42712,11 @@
           <t>Net finance costs (Note 10)</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OCEN.xlsx
+++ b/output/pdf_financials_xlsx/OCEN.xlsx
@@ -728,46 +728,46 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.010226</v>
+        <v>1.284353</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.124872</v>
+        <v>1.588922</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.68672</v>
+        <v>2.298216</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.958489</v>
+        <v>1.328663</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.927168</v>
+        <v>1.268888</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.243634</v>
+        <v>1.575868</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.407419</v>
+        <v>1.949775</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.124814</v>
+        <v>1.665219</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.385671</v>
+        <v>1.891346</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.058801</v>
+        <v>1.546434</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.488633</v>
+        <v>1.954675</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.641019</v>
+        <v>2.006841</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>4.813389</v>
+        <v>5.275195</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.871653</v>
+        <v>1.315047</v>
       </c>
     </row>
     <row r="8">
@@ -890,46 +890,46 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.010226</v>
+        <v>1.284353</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.124872</v>
+        <v>1.588922</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.68672</v>
+        <v>2.298216</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.958489</v>
+        <v>1.328663</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.927168</v>
+        <v>1.268888</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.401424</v>
+        <v>1.733658</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.573276</v>
+        <v>2.115632</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.570082</v>
+        <v>2.110487</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.397814</v>
+        <v>1.903489</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.067201</v>
+        <v>1.554834</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.488633</v>
+        <v>1.954675</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1.641019</v>
+        <v>2.006841</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>4.813389</v>
+        <v>5.275195</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.871653</v>
+        <v>1.315047</v>
       </c>
     </row>
     <row r="11">
@@ -1515,14 +1515,16 @@
       <c r="L20" s="3" t="n">
         <v>-6.54541</v>
       </c>
-      <c r="M20" s="3" t="n">
-        <v>-2.918392</v>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N20" s="3" t="n">
         <v>-6.357673</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-2.475671</v>
+        <v>-5.442671</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>-4.544425</v>
@@ -1570,13 +1572,13 @@
         <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>-2.918392</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>9.644348000000001</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>12.715668</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -3464,28 +3466,28 @@
         <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>36.619786</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>51.783149</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>43.081327</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>47.757327</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>47.757327</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>47.757327</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>47.757327</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>47.757327</v>
       </c>
       <c r="P56" s="3" t="n">
         <v>0</v>
@@ -3522,22 +3524,22 @@
         <v>0</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>0.018062</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>0.045534</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>0.076752</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>0.099846</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>0</v>
+        <v>0.117695</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>0</v>
+        <v>0.122157</v>
       </c>
       <c r="P57" s="3" t="n">
         <v>0</v>
@@ -3589,7 +3591,7 @@
         <v>5.052839</v>
       </c>
       <c r="O58" s="3" t="n">
-        <v>0</v>
+        <v>47.63517</v>
       </c>
       <c r="P58" s="3" t="n">
         <v>0</v>
@@ -3876,31 +3878,31 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.363778</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.571358</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>1.572045</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.158234</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.156731</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>2.039762</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>1.039355</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>1.389902</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.192564</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>0</v>
@@ -4032,43 +4034,43 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.362726</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.6481479999999999</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.298365</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.349425</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.347885</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>1.835256</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>4.730149</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>1.622127</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>1.425995</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.120567</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.198056</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.0445</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.190486</v>
       </c>
     </row>
     <row r="68">
@@ -6613,10 +6615,10 @@
         <v>0</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.086606</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-5.208541</v>
       </c>
       <c r="N116" s="3" t="n">
         <v>0</v>
@@ -20280,7 +20282,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -23027,7 +23033,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -25594,7 +25604,11 @@
           <t>Investment in the acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -28098,7 +28112,11 @@
           <t>Deferred income tax expenses</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -31431,7 +31449,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -34555,7 +34577,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -34691,7 +34717,11 @@
           <t>General office expenses</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -35679,7 +35709,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -35768,7 +35802,11 @@
           <t>Net income from discontinued operations (Note 6)</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -36654,7 +36692,11 @@
           <t>Net income from discontinued operations (Note 7 and 8)</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -38238,7 +38280,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -38873,7 +38915,11 @@
           <t>Net loss from discontinued operations (Note 6)</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -38930,7 +38976,7 @@
         </is>
       </c>
       <c r="P352" s="5" t="n">
-        <v>2.918392</v>
+        <v>-2.918392</v>
       </c>
       <c r="Q352" t="inlineStr">
         <is>
@@ -39415,7 +39461,11 @@
           <t>General and office expenses</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -45040,7 +45090,11 @@
           <t>Management, consulting and directors fees</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
